--- a/2022/North2/North2_Members_final.xlsx
+++ b/2022/North2/North2_Members_final.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>حركة العدالة والإنماء</t>
         </is>
       </c>
     </row>
